--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -8,25 +8,26 @@
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="심층분석 (계정별 Top) " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="총계정원장" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="벤포드 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="라운드넘버 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="계정별 상세거래내역" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="특수관계자 분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="리스완전성" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="손익월별分析" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="유형자산_처분손익" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="심층분석 (계정별 Top) " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="총계정원장" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="거래처 전기_당기 비교" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="상대계정 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="벤포드 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="라운드넘버 분석" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="매출 vs 비용 교차" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="계정별 상세거래내역" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="특수관계자 분석" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="리스완전성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="거래처분析" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="손익월별分析" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,13 +39,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,9 +71,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,12 +529,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>계정명</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>계정과목</t>
         </is>
       </c>
     </row>
@@ -544,23 +549,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>계정명</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>금액유형</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
+          <t>구분</t>
         </is>
       </c>
     </row>
@@ -575,16 +575,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>거래처명</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
+        <is>
+          <t>금액유형</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
@@ -607,7 +612,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>거래처명</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -627,13 +632,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
         </is>
       </c>
     </row>
@@ -648,40 +658,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>작업명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>계정과목</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
@@ -696,23 +679,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,6 +737,11 @@
         </is>
       </c>
       <c r="B1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
@@ -753,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,22 +769,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -794,41 +784,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>유형자산계정명</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>감가상각누계액계정명</t>
+          <t>금액열</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>대체상대계정</t>
+          <t>그룹기준열</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>취득원가_수동조정</t>
+          <t>실행여부</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>상각누계액_수동조정</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -845,688 +825,697 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>분석번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>분석명</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>분석대상</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>기준월</t>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>파라미터 시트명</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>필요 컬럼</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>작성방법</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>거래처 전기_당기 비교</t>
+          <t>(공통)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>분석목록 시트의 '분석명'은 아래 파라미터 시트명과 철자가 정확히 같아야 연결됩니다 (예: 분석명 '벤포드 분석' ↔ 시트명 '벤포드 분석'). 파라미터 시트 내 '실행여부' 열이 있는 경우 그 열이 Y(또는 O)인 행만 처리되고, 없는 시트는 적힌 행 전부가 처리됩니다.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>분석목록 자체의 실행여부는 메뉴 On/Off, 파라미터 시트의 실행여부는 그 메뉴 내 항목별 On/Off</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>벤포드 분석</t>
+          <t>거래처 전기_당기 비교</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분석 시트 참조</t>
+          <t>계정과목 / 금액열(차변·대변·both) / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>계정과목 한 줄에 하나씩. 지정한 방향(차변/대변)의 거래처별 전기·당기 금액을 비교표로 생성</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데이터 개요</t>
+          <t>벤포드 분석</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
+          <t>계정과목 / 금액열 / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>벤포드 법칙을 적용할 계정·방향 지정. 데이터 5건 미만이면 자동으로 "데이터 부족" 처리</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>계정명 리스트</t>
+          <t>(파라미터 시트 없음)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>분석목록에서 실행여부만 Y로 두면 전체 데이터 요약이 자동 생성됨</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>파라미터 불필요</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>사원별 집계</t>
+          <t>(파라미터 시트 없음)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>분석목록에서 실행여부만 Y로 두면 계정명 목록·통계가 자동 생성됨</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>파라미터 불필요</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>일자차이 분석</t>
+          <t>(파라미터 시트 없음)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분석 시트 참조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>사원명 컬럼을 자동 탐지해 집계 (컬럼명이 "사원명"이 아니면 preprocess.py에서 먼저 매핑 필요)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>파라미터 불필요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>상대계정 분석</t>
+          <t>일자차이 분석 (시트 미생성)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>특정 계정의 상대계정 분석 → 상대계정분석 시트 참조 (전표승인번호 기준 그룹핑)</t>
+          <t>기준일수 / 실행여부</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>쓰려면 시트명을 정확히 '일자차이 분석'으로 새로 만들고 기준일수(예: 30) 입력. 전표일자 대비 등록일자가 그 일수 이상 지연된 전표를 추출</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>등록일자 계열 컬럼이 있어야 동작</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>키워드 검색</t>
+          <t>상대계정 분석</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>적요 키워드 검색 → 키워드검색 시트 참조</t>
+          <t>계정과목 / 금액열 / 그룹기준열 / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>그룹기준열은 비워두면 전표그룹키(같은 전표를 묶는 내부 키)를 자동 사용 — 보통 비워두는 게 안전</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라운드넘버 분석</t>
+          <t>키워드검색 (시트 미생성)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
+          <t>키워드 / 실행여부</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>쓰려면 시트명을 정확히 '키워드검색'으로 새로 만들고 키워드를 한 줄씩 입력 (적요 컬럼에서 검색)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>특수관계자 분석</t>
+          <t>라운드넘버 분석</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>특수관계자 거래처 거래 추출 → 특수관계자 시트 참조 (거래처명 컬럼 없음, 사용불가)</t>
+          <t>계정과목 / 금액열 / 최소금액 / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
+          <t>계정과목에 '(전체)' 입력 시 전 계정 대상. 최소금액 이상 배수(10만/50만/100만/500만/1000만원)만 라운드로 탐지</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>자산 vs 부채 교차</t>
+          <t>특수관계자 분석</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>자산/부채 동시 발생 거래처 분석</t>
+          <t>거래처명 / 실행여부</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>거래처명은 부분일치 검색 (예: "판타지오" 입력 시 "(주)판타지오"도 매칭)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>매출 vs 비용 교차</t>
+          <t>자산 vs 부채 교차 (시트 미생성)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>매출/비용 동시 발생 거래처 분석</t>
+          <t>구분(자산/부채) / 계정과목</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>쓰려면 시트명을 정확히 '자산 vs 부채 교차'로 새로 만들고, 구분별 계정과목을 한 줄씩 입력</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>같은 거래처에서 자산·부채 계정이 동시에 발생하는 경우 추출</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>심층분석 (계정별 Top)</t>
+          <t>매출 vs 비용 교차</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>계정별 거래처 Top N 추출 → 심층분석 시트 참조</t>
+          <t>구분(매출/비용) / 계정과목</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>구분별로 계정과목을 한 줄씩 입력. 같은 거래처에서 매출·비용이 동시에 발생하는 경우를 찾음</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI 계정별 분석</t>
+          <t xml:space="preserve">심층분석 (계정별 Top) </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+          <t>계정과목 (선택: 개수 / 금액열 열 추가 가능)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>계정과목만 한 줄씩 나열해도 동작 (기본값: 상위 10건, 차대변 모두). 열을 추가하면 개수·방향 지정 가능</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>열 이름은 정확히 '개수', '금액열'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>데이터·헤더 확인</t>
+          <t>AI계정별분석 (시트 미생성)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>컬럼 인식 현황 점검 (파라미터 불필요)</t>
+          <t>계정과목 / 실행여부</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>쓰려면 시트명을 정확히 'AI계정별분석'으로 새로 만들고 계정과목 입력. Gemini 호출 없이 월별추이·샘플만 추출(26번과 형식은 같으나 AI 분석은 안 함)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>거래처 분석</t>
+          <t>(파라미터 시트 없음)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>특정 거래처 복합조건 상세 분석 → 거래처분석 시트 참조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>컬럼 인식 현황(O/X) 점검용. 실데이터 넣고 가장 먼저 돌려보면 좋음</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>파라미터 불필요</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>벤포드 이탈 상세 추출</t>
+          <t>거래처분析</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>벤포드 이탈 전표 상세 추출 → 벤포드이탈 시트 참조</t>
+          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>작업명은 자유 기재. 계정과목·거래처명은 콤마로 여러 개 지정 가능</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>월별 전계정 분석</t>
+          <t>벤포드이탈 (시트 미생성)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>전 계정 월별 차변/대변 집계 (파라미터 불필요)</t>
+          <t>계정과목 / 금액열 / 임계값 / 최대건수 / 실행여부</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>쓰려면 시트명을 정확히 '벤포드이탈'로 새로 만들 것. 벤포드 법칙에서 크게 벗어난 전표를 상세 추출</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>잔액증감분석 (계정별 거래처별)</t>
+          <t>(파라미터 시트 없음)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>각 계정별 거래처별로 기초잔액 증가 감소 기말 잔액 추출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>전 계정 월별 차변/대변 집계가 자동 생성됨</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>파라미터 불필요</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>총계정원장</t>
+          <t>잔액증감분석 (게정별 거래처벌)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>전기/당기/전당기 기간의 계정별 월별합계 차/대/전체로 추출</t>
+          <t>계정명 / 구분(차변·대변 또는 자산·부채)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>data/previous 폴더에 전기 "계정별_거래처별명세" 파일이 있어야 기초잔액이 채워짐 (없으면 오류 시트만 생성)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>은행조회서 완전성</t>
+          <t>총계정원장</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>이자비용, 장단기차입금, 전환사채, RCPS등의 거래처와 은행조회서 발송내역 비교</t>
+          <t>구분 / 계정과목</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>구분은 시트명 접두어로만 쓰이는 자유 기재 항목(예: 자산/부채). data에 연도가 2개 이상 섞여 있으면 연도비교 표로 자동 전환</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>계정별 상세거래내역</t>
+          <t>은행조회서 완전성</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>각 계정별로 계정과목 차변/대변/차변대변모두 를 선택하여 데이터추출</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>비워두면 기본 계정(이자비용/단기차입금/장기차입금/전환사채 등)을 자동 사용</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>리스완전성</t>
+          <t>계정별 상세거래내역</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K-IFRS 116호 리스 인식 대상 완전성 검토</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>계정과목 / 금액유형(차변·대변·차변대변모두) / 실행여부</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손익월별分析</t>
+          <t>리스완전성</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>손익 계정별 전기/당기 차변·대변 선택 비교 (월별 + 거래처별)</t>
+          <t>계정과목 / 실행여부</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>비워두면 기본 계정(임차료/지급수수료/차량유지비/건물관리비/렌탈)을 자동 사용</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>결과는 별도 파일로 저장됨</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AI계정별분석_실행</t>
+          <t>손익월별分析</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립 실행)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>당기</t>
-        </is>
-      </c>
+          <t>계정과목 / 구분(차변·대변·both) / 실행여부</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AI계정별분석_실행</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>계정과목 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 비용 발생)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>감가상각_평가손익분석</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>당기</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열 / 그룹기준열 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>★계정과목에는 유형자산명이 아니라 '손익 계정명'을 적음 (예: 감가상각비, 외화환산손익, 평가손익, 대손상각비). 8번 상대계정분석과 완전히 동일한 로직(Phase 1)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>유형자산 롤포워드/처분손익은 아래 두 시트로 별도 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>27-Phase2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>감가상각_유형자산롤포워드</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>유형자산계정명 / 감가상각누계액계정명 / 대체상대계정 / 취득원가_수동조정 / 상각누계액_수동조정 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>27번이 실행여부 Y이고 이 시트에서 실행여부 Y인 행이 있으면 자동 실행됨 (분석목록에 별도 번호 없음). 대체상대계정은 계정대체가 있을 때만 입력(콤마로 여러 개 가능), 없으면 비워둠. 수동조정 2종은 전표매칭으로 못 잡는 잔여차이를 감사인이 직접 숫자로 입력(기본 0)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>비워두면(실행여부 Y행 0개) 조용히 건너뛰고 27번은 Phase1만 결과로 나옴 — 에러 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>27-Phase3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>유형자산_처분손익</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>처분이익계정명 / 처분손실계정명 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>27번 + 위 롤포워드 시트가 모두 있어야 자동 실행됨. 처분이익·처분손실 계정이 등장한 전표마다 같은 전표의 유형자산 취득원가·감가상각누계액을 찾아 처분 건별로 한 줄씩 명세 생성</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>개별 자산이 아닌 계정과목×전표 단위로만 구분됨 — 한 전표에 여러 자산을 묶어 처분하면 한 줄로 잡힘</t>
         </is>
       </c>
     </row>
@@ -1541,6 +1530,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>유형자산계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>감가상각누계액계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>대체상대계정</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>취득원가_수동조정</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상각누계액_수동조정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1577,13 +1617,688 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>분석번호</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>분석명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>분석대상</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기준월</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>거래처 전기_당기 비교</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>벤포드 분석</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분석 시트 참조</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>데이터 개요</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>계정명 리스트</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>사원별 집계</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>일자차이 분석</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분석 시트 참조</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>상대계정 분석</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>특정 계정의 상대계정 분석 → 상대계정분석 시트 참조 (전표승인번호 기준 그룹핑)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>키워드 검색</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>적요 키워드 검색 → 키워드검색 시트 참조</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>라운드넘버 분석</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>특수관계자 분석</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>특수관계자 거래처 거래 추출 → 특수관계자 시트 참조 (거래처명 컬럼 없음, 사용불가)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>자산 vs 부채 교차</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>자산/부채 동시 발생 거래처 분석</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>매출 vs 비용 교차</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>매출/비용 동시 발생 거래처 분석</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>심층분석 (계정별 Top)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>계정별 거래처 Top N 추출 → 심층분석 시트 참조</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AI 계정별 분석</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>데이터·헤더 확인</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>컬럼 인식 현황 점검 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>거래처 분석</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>특정 거래처 복합조건 상세 분석 → 거래처분석 시트 참조</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>벤포드 이탈 상세 추출</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>벤포드 이탈 전표 상세 추출 → 벤포드이탈 시트 참조</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>월별 전계정 분석</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>전 계정 월별 차변/대변 집계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>잔액증감분석 (계정별 거래처별)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>각 계정별 거래처별로 기초잔액 증가 감소 기말 잔액 추출</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>총계정원장</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>전기/당기/전당기 기간의 계정별 월별합계 차/대/전체로 추출</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>은행조회서 완전성</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>이자비용, 장단기차입금, 전환사채, RCPS등의 거래처와 은행조회서 발송내역 비교</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>계정별 상세거래내역</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>각 계정별로 계정과목 차변/대변/차변대변모두 를 선택하여 데이터추출</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>리스완전성</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>K-IFRS 116호 리스 인식 대상 완전성 검토</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>손익월별分析</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>손익 계정별 전기/당기 차변·대변 선택 비교 (월별 + 거래처별)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AI계정별분석_실행</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립 실행)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>감가상각_평가손익분석</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -1598,16 +2313,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
@@ -1624,28 +2334,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1660,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1676,39 +2376,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>그룹기준열</t>
+          <t>실행여부</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>여비교통비-식대</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>그룹기준열 비워두면 전표그룹키(=전표승인번호) 자동 사용 — 샘플 4행 기준 미지급금-카드가 상대계정으로 잡히는지 확인용 예시</t>
         </is>
       </c>
     </row>
@@ -1723,7 +2396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,12 +2412,39 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>여비교통비-식대</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>그룹기준열 비워두면 전표그룹키(=전표승인번호) 자동 사용 — 샘플 4행 기준 미지급금-카드가 상대계정으로 잡히는지 확인용 예시</t>
         </is>
       </c>
     </row>
@@ -1759,7 +2459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1775,62 +2475,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>최소금액</t>
+          <t>실행여부</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10억원 이상 라운드 수 탐지</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
@@ -1845,18 +2495,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>최소금액</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10억원 이상 라운드 수 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -22,8 +22,8 @@
     <sheet name="특수관계자 분석" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="리스완전성" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="거래처분析" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="손익월별分析" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="거래처분석" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="손익월별분석" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
@@ -906,7 +906,6 @@
           <t>계정과목 한 줄에 하나씩. 지정한 방향(차변/대변)의 거래처별 전기·당기 금액을 비교표로 생성</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -927,7 +926,6 @@
           <t>벤포드 법칙을 적용할 계정·방향 지정. 데이터 5건 미만이면 자동으로 "데이터 부족" 처리</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1048,7 +1046,6 @@
           <t>그룹기준열은 비워두면 전표그룹키(같은 전표를 묶는 내부 키)를 자동 사용 — 보통 비워두는 게 안전</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1069,7 +1066,6 @@
           <t>쓰려면 시트명을 정확히 '키워드검색'으로 새로 만들고 키워드를 한 줄씩 입력 (적요 컬럼에서 검색)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1090,7 +1086,6 @@
           <t>계정과목에 '(전체)' 입력 시 전 계정 대상. 최소금액 이상 배수(10만/50만/100만/500만/1000만원)만 라운드로 탐지</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1111,7 +1106,6 @@
           <t>거래처명은 부분일치 검색 (예: "판타지오" 입력 시 "(주)판타지오"도 매칭)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1157,7 +1151,6 @@
           <t>구분별로 계정과목을 한 줄씩 입력. 같은 거래처에서 매출·비용이 동시에 발생하는 경우를 찾음</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1203,7 +1196,6 @@
           <t>쓰려면 시트명을 정확히 'AI계정별분석'으로 새로 만들고 계정과목 입력. Gemini 호출 없이 월별추이·샘플만 추출(26번과 형식은 같으나 AI 분석은 안 함)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1236,7 +1228,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>거래처분析</t>
+          <t>거래처분석</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1249,7 +1241,6 @@
           <t>작업명은 자유 기재. 계정과목·거래처명은 콤마로 여러 개 지정 가능</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1270,7 +1261,6 @@
           <t>쓰려면 시트명을 정확히 '벤포드이탈'로 새로 만들 것. 벤포드 법칙에서 크게 벗어난 전표를 상세 추출</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1316,7 +1306,6 @@
           <t>data/previous 폴더에 전기 "계정별_거래처별명세" 파일이 있어야 기초잔액이 채워짐 (없으면 오류 시트만 생성)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1337,7 +1326,6 @@
           <t>구분은 시트명 접두어로만 쓰이는 자유 기재 항목(예: 자산/부채). data에 연도가 2개 이상 섞여 있으면 연도비교 표로 자동 전환</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1358,7 +1346,6 @@
           <t>비워두면 기본 계정(이자비용/단기차입금/장기차입금/전환사채 등)을 자동 사용</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1374,8 +1361,6 @@
           <t>계정과목 / 금액유형(차변·대변·차변대변모두) / 실행여부</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1408,7 +1393,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>손익월별分析</t>
+          <t>손익월별분석</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1416,8 +1401,6 @@
           <t>계정과목 / 구분(차변·대변·both) / 실행여부</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1438,7 +1421,6 @@
           <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 비용 발생)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2233,7 +2215,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손익월별分析</t>
+          <t>손익월별분석</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,6 +744,11 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>손익구분</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -30,25 +29,36 @@
     <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -71,13 +81,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -149,6 +160,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>감사자동화</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>본사 / 2공장 등 전표관리단위 값을 적으면 해당 단위 데이터만으로 분석 실행 (공란=전체, samdong 전용 컬럼)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>감사자동화</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Y로 지정하면 원장의 전표관리단위(본사/2공장 등) 컬럼 기준으로 거래처별 금액을 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,7 +482,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="17.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="88.4140625" bestFit="1" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -483,7 +528,7 @@
           <t>StartDate</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -498,7 +543,7 @@
           <t>EndDate</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -524,7 +569,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -550,7 +595,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -576,7 +621,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -607,7 +652,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -633,7 +678,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -659,7 +704,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -680,7 +725,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -728,7 +773,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -764,7 +809,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -790,7 +835,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -831,7 +876,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -1518,7 +1563,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1569,7 +1614,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1604,8 +1649,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="28.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="85.9140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="6" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1638,6 +1688,11 @@
           <t>기준월</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>관리단위</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1655,7 +1710,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1680,7 +1735,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1805,7 +1860,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1855,7 +1910,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1880,7 +1935,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1930,7 +1985,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1955,7 +2010,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1980,7 +2035,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2030,7 +2085,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2105,7 +2160,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2155,7 +2210,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2180,7 +2235,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2230,7 +2285,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2255,7 +2310,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2280,7 +2335,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2291,6 +2346,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2300,13 +2356,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외화외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>받을어음</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>부도어음</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2409,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2347,8 +2434,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="10.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2371,9 +2464,71 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>관리단위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2384,7 +2539,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2447,7 +2602,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2483,7 +2638,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -163,21 +163,6 @@
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>감사자동화</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>본사 / 2공장 등 전표관리단위 값을 적으면 해당 단위 데이터만으로 분석 실행 (공란=전체, samdong 전용 컬럼)</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>감사자동화</author>
@@ -1649,7 +1634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="28.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -1688,11 +1673,6 @@
           <t>기준월</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>관리단위</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2346,7 +2326,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="15" activeTab="15" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -171,6 +171,21 @@
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>Y로 지정하면 원장의 전표관리단위(본사/2공장 등) 컬럼 기준으로 거래처별 금액을 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>감사자동화</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Y로 지정하면 해당 계정의 월별 금액을 전표관리단위(본사/2공장 등)별로 나눈 행을 함께 추출 (공란=기존처럼 단위 구분 없이 1행)</t>
       </text>
     </comment>
   </commentList>
@@ -757,8 +772,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -781,9 +800,15 @@
           <t>손익구분</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>관리단위</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2416,10 +2441,9 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="10.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="8.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -178,6 +178,21 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>감사자동화</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>감사자동화</author>
@@ -724,8 +739,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -753,6 +772,11 @@
           <t>실행여부</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>관리단위</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -763,6 +787,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="15" activeTab="15" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -173,6 +173,11 @@
         <t>Y로 지정하면 원장의 전표관리단위(본사/2공장 등) 컬럼 기준으로 거래처별 금액을 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
       </text>
     </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Y로 지정하면 원장의 비용구분(판관/제조 등) 컬럼 기준으로 거래처별 금액을 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -183,9 +188,9 @@
     <author>감사자동화</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
+        <t>Y로 지정하면 이 계정의 상세를 비용구분(판관/제조 등)별로도 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
       </text>
     </comment>
   </commentList>
@@ -200,7 +205,32 @@
   <commentList>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
+        <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Y로 지정하면 이 작업의 월별합산 결과를 비용구분(판관/제조 등)별로도 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>감사자동화</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
         <t>Y로 지정하면 해당 계정의 월별 금액을 전표관리단위(본사/2공장 등)별로 나눈 행을 함께 추출 (공란=기존처럼 단위 구분 없이 1행)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Y로 지정하면 해당 계정의 월별 금액을 비용구분(판관/제조 등)별로 나눈 행을 함께 추출 (공란=기존처럼 구분 없이 1행)</t>
       </text>
     </comment>
   </commentList>
@@ -583,8 +613,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -597,9 +631,106 @@
           <t>계정과목</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>비용구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>반제품매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MB매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>부산물매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -739,11 +870,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20.08203125" customWidth="1" min="1" max="1"/>
+    <col width="26.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="35.25" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="5" max="6"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -777,11 +912,97 @@
           <t>관리단위</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>비용구분</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>농협경제지주</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>제품매출_국내, 상품매출_국내</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>농협경제지주</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>국보화학</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>제품매출_국내, 상품매출_국내</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>국보화학</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>국보화학(2공장)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>제품매출_국내, 상품매출_국내</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>국보화학(2공장)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -797,11 +1018,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="6"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,6 +1050,11 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>관리단위</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>비용구분</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2690,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="8.5" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2495,6 +2724,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>관리단위</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>비용구분</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="13" activeTab="16" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -35,10 +35,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -60,6 +61,13 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -78,17 +86,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -223,6 +240,26 @@
     <author>감사자동화</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>원장 계정명을 입력 (부분일치도 인식되지만, 표기가 다르면 엉뚱한 계정으로 유사매칭될 수 있으니 원장의 정확한 계정명을 그대로 적을 것. 예: 제품매출-국내)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>차변/대변/both 중 하나 — 이 계정 금액을 어느 열에서 집계할지 지정. 매출·영업외수익 계정은 대변, 매출원가·판관비·영업외비용 계정은 차변. 공란이면 자동으로 대변 처리되므로 비용 계정은 반드시 차변을 명시해야 함(안 그러면 결과가 0으로 비어버림)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>매출/매출원가/판관비/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐(예: 손익구분=판관비 → 손익월별_판관비 시트). 공란이면 구분(차변/대변)으로 매출·판관비만 자동 추정하므로, 매출원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함</t>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Y로 지정하면 해당 계정의 월별 금액을 전표관리단위(본사/2공장 등)별로 나눈 행을 함께 추출 (공란=기존처럼 단위 구분 없이 1행)</t>
@@ -573,7 +610,7 @@
           <t>StartDate</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -588,7 +625,7 @@
           <t>EndDate</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -613,10 +650,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="23" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -725,6 +762,883 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>비용</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>교육훈련비</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>도서인쇄비</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>복리후생비-경조비</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>복리후생비-기숙사운영</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>복리후생비-기타</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>복리후생비-선물비</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>복리후생비-식당운영</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>복리후생비-식대</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>복리후생비-행사비</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>소모품비-공구소모품</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>소모품비-기타</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>소모품비-사무용품</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>소모품비-생산소모품</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>소모품비-전산용품</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>수도광열비-MB실</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>수도광열비-기숙사</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>수도광열비-기타</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>수도광열비-식당</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>수선비-건물</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>수선비-공구와기구</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>수선비-구축물</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>수선비-기계장치</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>수선비-기타</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>여비교통비-교통비</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>여비교통비-기타</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>여비교통비-숙박비</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>여비교통비-식대</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>운반비-원료</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>운반비-제품</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>전력비</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>접대비-경조사</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>접대비-기타</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>접대비-별도</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>접대비-식대등</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>접대비-주대</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>접대비-체력단련</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>지급수수료-계통</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>지급수수료-기타</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>지급수수료-수탁수수료</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>지급수수료-안전관리</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>지급수수료-용역료</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>지급수수료-은행수수료</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>지급수수료-자문료</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>지급수수료-장려금</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>지급수수료-재활용분담금</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>지급수수료-파렛트사용료</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>지급수수료-판매</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>포장비</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>회의비</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -876,9 +1790,7 @@
     <col width="20.08203125" customWidth="1" min="1" max="1"/>
     <col width="26.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="35.25" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="5" max="6"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="5" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,12 +1930,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13" customWidth="1" min="5" max="6"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="5" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1055,6 +1966,1569 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>비용구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>반제품매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MB매출</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>부산물매출</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>교육훈련비</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>도서인쇄비</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>복리후생비-경조비</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>복리후생비-기숙사운영</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>복리후생비-기타</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>복리후생비-선물비</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>복리후생비-식당운영</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>복리후생비-식대</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>복리후생비-행사비</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>소모품비-공구소모품</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>소모품비-기타</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>소모품비-사무용품</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>소모품비-생산소모품</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>소모품비-전산용품</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>수도광열비-MB실</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>수도광열비-기숙사</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>수도광열비-기타</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>수도광열비-식당</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>수선비-건물</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>수선비-공구와기구</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>수선비-구축물</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>수선비-기계장치</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>수선비-기타</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>여비교통비-교통비</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>여비교통비-기타</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>여비교통비-숙박비</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>여비교통비-식대</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>운반비-원료</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>운반비-제품</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>전력비</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>접대비-경조사</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>접대비-기타</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>접대비-별도</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>접대비-식대등</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>접대비-주대</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>접대비-체력단련</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>지급수수료-계통</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>지급수수료-기타</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>지급수수료-수탁수수료</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>지급수수료-안전관리</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>지급수수료-용역료</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>지급수수료-은행수수료</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>지급수수료-자문료</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>지급수수료-장려금</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>지급수수료-재활용분담금</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>지급수수료-파렛트사용료</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>지급수수료-판매</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>포장비</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>회의비</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2417,7 +4891,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2612,7 +5086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2650,6 +5124,41 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>부도어음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
         </is>
       </c>
     </row>
@@ -2690,14 +5199,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="8.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="5"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2738,6 +5245,11 @@
           <t>외상매입금</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2783,6 +5295,347 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>지급수수료-계통</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>지급수수료-기타</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>지급수수료-수탁수수료</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>지급수수료-안전관리</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>지급수수료-용역료</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>지급수수료-은행수수료</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>지급수수료-자문료</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>지급수수료-장려금</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>지급수수료-재활용분담금</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>지급수수료-파렛트사용료</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>지급수수료-판매</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2800,8 +5653,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="15.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2833,22 +5690,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>여비교통비-식대</t>
+          <t>제품매출-국내</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>그룹기준열 비워두면 전표그룹키(=전표승인번호) 자동 사용 — 샘플 4행 기준 미지급금-카드가 상대계정으로 잡히는지 확인용 예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2863,8 +5805,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2887,6 +5832,114 @@
           <t>비고</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2899,8 +5952,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="14.25" bestFit="1" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2940,12 +5997,12 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>1000000000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2965,12 +6022,72 @@
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>1000000000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -185,6 +185,26 @@
     <author>감사자동화</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>원장 계정명을 입력 (부분일치도 인식되지만, 표기가 다르면 엉뚱한 계정으로 유사매칭될 수 있으니 원장의 정확한 계정명을 그대로 적을 것. 예: 제품매출-국내)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>차변/대변/both 중 하나 — 이 계정의 거래처별 금액을 어느 열에서 집계할지 지정. 매출 등 대변 계정은 대변, 매입채무 등 차변 계정은 차변으로 입력. 공란이면 자동으로 차변 처리됨(주의: 손익월별분석 시트의 구분 컬럼은 공란일 때 대변이 기본값이라 반대이니 헷갈리지 말 것)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>자유 기재란 — 분석 로직에는 사용되지 않음 (메모용)</t>
+      </text>
+    </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>Y로 지정하면 원장의 전표관리단위(본사/2공장 등) 컬럼 기준으로 거래처별 금액을 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -240,6 +240,31 @@
     <author>감사자동화</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>이 작업의 결과 시트 이름으로 쓰일 자유 기재란(예: 국보화학 → 거래처_국보화학 시트 생성). 공란이면 거래처01, 거래처02...로 자동 부여됨</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>원장 계정명을 입력, 콤마(,)로 여러 개 지정 가능 (예: 제품매출-국내, 제품매출-수출). 공란이나 (전체)로 두면 계정 제한 없이 거래처명만으로 필터링. 부분일치도 인식되지만 표기가 다르면 엉뚱한 계정으로 유사매칭될 수 있으니 원장의 정확한 계정명을 그대로 적을 것</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>원장 거래처명을 입력, 콤마(,)로 여러 개 지정 가능. 부분일치(포함) 방식이라 일부만 적어도 매칭됨. 필수 입력 — 공란이면 이 행 전체가 무시됨</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>차변/대변/both 중 하나 — 상세내역·월별합산에 포함할 금액 방향. 공란이면 자동으로 both(차변+대변 모두) 처리됨</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -302,7 +302,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>매출/매출원가/판관비/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐(예: 손익구분=판관비 → 손익월별_판관비 시트). 공란이면 구분(차변/대변)으로 매출·판관비만 자동 추정하므로, 매출원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함</t>
+        <t>매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐(예: 손익구분=판관비 → 손익월별_판관비 시트). 공란이면 구분(차변/대변)으로 매출·판관비만 자동 추정하므로, 매출원가·제조원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함. 셀 클릭 시 드롭다운으로 선택 가능</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -3578,6 +3578,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
+      <formula1>"매출,매출원가,판관비,제조원가,영업외수익,영업외비용"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -302,7 +302,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐(예: 손익구분=판관비 → 손익월별_판관비 시트). 공란이면 구분(차변/대변)으로 매출·판관비만 자동 추정하므로, 매출원가·제조원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함. 셀 클릭 시 드롭다운으로 선택 가능</t>
+        <t>매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐. 판관비와 제조원가는 손익구분 단계에서 명확히 나누기 어려워 하나의 카테고리(판관비/제조원가)로 통합했고, 실제 판관/제조 구분이 필요하면 비용구분(Y) 옵션으로 원장 값 기준 같은 시트 안에서 행을 나눔. 손익구분을 판관비 또는 제조원가로만 적어도 자동으로 판관비/제조원가로 인식됨. 공란이면 구분(차변/대변)으로 매출·판관비/제조원가만 자동 추정하므로, 매출원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함. 셀 클릭 시 드롭다운으로 선택 가능</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>판관비/제조원가</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
-      <formula1>"매출,매출원가,판관비,제조원가,영업외수익,영업외비용"</formula1>
+      <formula1>"매출,매출원가,판관비/제조원가,영업외수익,영업외비용"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -302,7 +302,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐. 판관비와 제조원가는 손익구분 단계에서 명확히 나누기 어려워 하나의 카테고리(판관비/제조원가)로 통합했고, 실제 판관/제조 구분이 필요하면 비용구분(Y) 옵션으로 원장 값 기준 같은 시트 안에서 행을 나눔. 손익구분을 판관비 또는 제조원가로만 적어도 자동으로 판관비/제조원가로 인식됨. 공란이면 구분(차변/대변)으로 매출·판관비/제조원가만 자동 추정하므로, 매출원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함. 셀 클릭 시 드롭다운으로 선택 가능</t>
+        <t>매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 하나 — 이 값에 따라 결과가 들어갈 시트가 정해짐. 계정 자체로 판관비/제조원가가 명확히 구분되는 회사는 각각 직접 적어 별도 시트로 뽑으면 됨. samdong처럼 계정만으로는 판관/제조가 갈리지 않는 회사는 여기엔 일괄 판관비만 적고, 실제 판관/제조 구분은 비용구분(Y) 옵션으로 원장 값을 반영해 같은 시트 안에서 행을 나눔. 공란이면 구분(차변/대변)으로 매출·판관비만 자동 추정하므로, 매출원가·제조원가·영업외수익·영업외비용으로 분류하려면 반드시 직접 입력해야 함. 셀 클릭 시 드롭다운으로 선택 가능</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>판관비/제조원가</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
-      <formula1>"매출,매출원가,판관비/제조원가,영업외수익,영업외비용"</formula1>
+      <formula1>"매출,매출원가,판관비,제조원가,영업외수익,영업외비용"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/journal_analyzer/samdong/task_list_samdong.xlsx
+++ b/journal_analyzer/samdong/task_list_samdong.xlsx
@@ -3,28 +3,28 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="13" activeTab="16" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="13" activeTab="15" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="심층분석 (계정별 Top) " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="총계정원장" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="상대계정 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="벤포드 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="라운드넘버 분석" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="매출 vs 비용 교차" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="계정별 상세거래내역" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="특수관계자 분석" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="리스완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="거래처분석" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="손익월별분석" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="17_거래처분석" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="21_총계정원장" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="22_은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="24_리스완전성" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="25_손익월별분석" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
@@ -695,993 +695,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="23" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>계정과목</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>비용구분</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>상품매출-국내</t>
+          <t>외상매출금</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>상품매출-수출</t>
+          <t>외화외상매출금</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>제품매출-국내</t>
+          <t>받을어음</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>제품매출-수출</t>
+          <t>부도어음</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>반제품매출</t>
+          <t>외상매입금</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MB매출</t>
+          <t>상품매출-국내</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>부산물매출</t>
+          <t>상품매출-수출</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>광고선전비</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>제품매출-국내</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>교육훈련비</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>도서인쇄비</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>복리후생비-경조비</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>복리후생비-기숙사운영</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>복리후생비-기타</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>복리후생비-선물비</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>복리후생비-식당운영</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>복리후생비-식대</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>복리후생비-행사비</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>소모품비-공구소모품</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>소모품비-기타</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>소모품비-사무용품</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>소모품비-생산소모품</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>소모품비-전산용품</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>소프트웨어</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>수도광열비-MB실</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>수도광열비-기숙사</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>수도광열비-기타</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>수도광열비-식당</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>수선비-건물</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>수선비-공구와기구</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>수선비-구축물</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>수선비-기계장치</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>수선비-기타</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>여비교통비-교통비</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>여비교통비-기타</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>여비교통비-숙박비</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>여비교통비-식대</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>운반비-원료</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>운반비-제품</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>전력비</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>접대비-경조사</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>접대비-기타</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>접대비-별도</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>접대비-식대등</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>접대비-주대</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>접대비-체력단련</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>지급수수료-계통</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>지급수수료-기타</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>지급수수료-수탁수수료</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>지급수수료-안전관리</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>지급수수료-용역료</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>지급수수료-은행수수료</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>지급수수료-자문료</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>지급수수료-장려금</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>지급수수료-재활용분담금</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>지급수수료-파렛트사용료</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>지급수수료-판매</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>지급임차료</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>포장비</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>회의비</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="20.08203125" customWidth="1" min="1" max="1"/>
+    <col width="26.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="35.25" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="5" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>관리단위</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>비용구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>농협경제지주</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>제품매출-국내, 상품매출-국내</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>농협경제지주</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>국보화학</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>제품매출-국내, 상품매출-국내</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>국보화학</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>국보화학(2공장)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>제품매출-국내, 상품매출-국내</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>국보화학(2공장)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1693,7 +937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1711,37 +955,6 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>구분</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액유형</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
         </is>
       </c>
     </row>
@@ -1762,12 +975,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>거래처명</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>실행여부</t>
+          <t>계정과목</t>
         </is>
       </c>
     </row>
@@ -1782,8 +995,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1791,9 +1007,130 @@
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>당좌예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>만기보유증권</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>매도가능증권</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>받을어음 대손충당금</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>받을어음-가계수표</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>받을어음-당좌수표</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>받을어음-약속어음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>받을어음-전자어음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>사채이자</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>지급수수료-은행수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>이자비용-구매자금</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>이자비용-대출보증</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>이자비용-일반대출</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>이자수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>보험료-차량보험</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>보험료-화재보험</t>
         </is>
       </c>
     </row>
@@ -1808,13 +1145,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액유형</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
         </is>
       </c>
     </row>
@@ -1829,143 +1176,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="20.08203125" customWidth="1" min="1" max="1"/>
-    <col width="26.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35.25" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="5" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>작업명</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>실행여부</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>관리단위</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>비용구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>농협경제지주</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>제품매출_국내, 상품매출_국내</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>농협경제지주</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>국보화학</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>제품매출_국내, 상품매출_국내</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>국보화학</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>국보화학(2공장)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>제품매출_국내, 상품매출_국내</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>국보화학(2공장)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1975,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2172,11 +1399,15 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="H8">
+        <f>_xlfn.TEXTJOIN(",",TRUE,uniue(_xlfn.TOROW(A9:A102)))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>감가상각비-건물</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2203,7 +1434,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>교육훈련비</t>
+          <t>감가상각비-공구와기구</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2230,7 +1461,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>도서인쇄비</t>
+          <t>감가상각비-구축물</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2257,7 +1488,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>복리후생비-경조비</t>
+          <t>감가상각비-기계장치</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2284,7 +1515,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>복리후생비-기숙사운영</t>
+          <t>감가상각비-비품</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2311,7 +1542,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>복리후생비-기타</t>
+          <t>감가상각비-차량운반구</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2338,7 +1569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>복리후생비-선물비</t>
+          <t>경상연구개발비-급여</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2365,7 +1596,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>복리후생비-식당운영</t>
+          <t>경상연구개발비-기타</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2392,7 +1623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>복리후생비-식대</t>
+          <t>경상연구개발비-상여</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2419,7 +1650,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>복리후생비-행사비</t>
+          <t>경상연구개발비-셈플</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2446,7 +1677,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>소모품비-공구소모품</t>
+          <t>경상연구개발비-출장경비</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2473,7 +1704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>소모품비-기타</t>
+          <t>광고선전비</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2500,7 +1731,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>소모품비-사무용품</t>
+          <t>교육훈련비</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2527,7 +1758,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>소모품비-생산소모품</t>
+          <t>대손상각비-받을어음</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2554,7 +1785,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>소모품비-전산용품</t>
+          <t>대손상각비-외상매출금</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2581,7 +1812,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>대손상각비-외화외상매출금</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2608,7 +1839,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>수도광열비-MB실</t>
+          <t>도서인쇄비</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2635,7 +1866,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>수도광열비-기숙사</t>
+          <t>매출채권처분손실</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,7 +1881,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>영업외비용</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2662,7 +1893,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>수도광열비-기타</t>
+          <t>무형자산감가상각비</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2689,7 +1920,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>수도광열비-식당</t>
+          <t>보험료-건강보험</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2716,7 +1947,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>수선비-건물</t>
+          <t>보험료-고용보험</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2743,7 +1974,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>수선비-공구와기구</t>
+          <t>보험료-보증보험</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2770,7 +2001,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>수선비-구축물</t>
+          <t>보험료-산재보험</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2797,7 +2028,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>수선비-기계장치</t>
+          <t>보험료-차량보험</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,7 +2055,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>수선비-기타</t>
+          <t>보험료-화재보험</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2851,7 +2082,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>여비교통비-교통비</t>
+          <t>복리후생비-경조비</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2878,7 +2109,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>여비교통비-기타</t>
+          <t>복리후생비-기숙사운영</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2905,7 +2136,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>여비교통비-숙박비</t>
+          <t>복리후생비-기타</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2932,7 +2163,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>여비교통비-식대</t>
+          <t>복리후생비-선물비</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2959,7 +2190,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>운반비-원료</t>
+          <t>복리후생비-식당운영</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2986,7 +2217,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>운반비-제품</t>
+          <t>복리후생비-식대</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3013,7 +2244,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>전력비</t>
+          <t>복리후생비-행사비</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3040,7 +2271,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>접대비-경조사</t>
+          <t>사채이자</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3055,7 +2286,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>영업외비용</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3067,7 +2298,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>접대비-기타</t>
+          <t>세금과공과-국민연금</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3094,7 +2325,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>접대비-별도</t>
+          <t>세금과공과-기타</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3121,7 +2352,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>접대비-식대등</t>
+          <t>세금과공과-면허세</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3148,7 +2379,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>접대비-주대</t>
+          <t>세금과공과-인지세</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3175,7 +2406,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>접대비-체력단련</t>
+          <t>세금과공과-재산세</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3202,7 +2433,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>지급수수료-계통</t>
+          <t>세금과공과-지방소득세</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3229,7 +2460,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>지급수수료-기타</t>
+          <t>세금과공과-지하수이용부담금</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3256,7 +2487,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>지급수수료-수탁수수료</t>
+          <t>세금과공과-차량범칙금</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3283,7 +2514,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>지급수수료-안전관리</t>
+          <t>소모품비-공구소모품</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3310,7 +2541,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>지급수수료-용역료</t>
+          <t>소모품비-기타</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3337,7 +2568,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>지급수수료-은행수수료</t>
+          <t>소모품비-사무용품</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3364,7 +2595,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>지급수수료-자문료</t>
+          <t>소모품비-생산소모품</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3391,7 +2622,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>지급수수료-장려금</t>
+          <t>소모품비-전산용품</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3418,7 +2649,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>지급수수료-재활용분담금</t>
+          <t>소프트웨어</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3445,7 +2676,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>지급수수료-파렛트사용료</t>
+          <t>수도광열비-MB실</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3472,7 +2703,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>지급수수료-판매</t>
+          <t>수도광열비-기숙사</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3499,7 +2730,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>지급임차료</t>
+          <t>수도광열비-기타</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3526,7 +2757,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>포장비</t>
+          <t>수도광열비-식당</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3553,27 +2784,1265 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>수선비-건물</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>수선비-공구와기구</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>수선비-구축물</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>수선비-기계장치</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>수선비-기타</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>여비교통비-교통비</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>여비교통비-기타</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>여비교통비-숙박비</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>여비교통비-식대</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>운반비-원료</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>운반비-제품</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>임대료수입</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>잡손실</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>영업외비용</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>잡이익</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>영업외수익</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>전력비</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>전력비</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>접대비-경조사</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>접대비-기타</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>접대비-별도</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>접대비-식대등</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>접대비-주대</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>접대비-체력단련</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>지급수수료-계통</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>지급수수료-기타</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>지급수수료-수탁수수료</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>지급수수료-안전관리</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>지급수수료-용역료</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>지급수수료-은행수수료</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>지급수수료-자문료</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>지급수수료-장려금</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>지급수수료-재활용분담금</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>지급수수료-파렛트사용료</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>지급수수료-판매</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>차량유지비-기타</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>차량유지비-렌탈료</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>차량유지비-수리비</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>차량유지비-유류대</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>차량유지비-통행료</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>통신비-일반</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>퇴직급여</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>포장비</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>회의비</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>판관비</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>영업외수익</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>영업외수익</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>이자비용-구매자금</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>영업외비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>이자비용-대출보증</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>영업외비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>이자비용-일반대출</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>영업외비용</t>
         </is>
       </c>
     </row>
@@ -3584,6 +4053,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -3594,8 +4064,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3606,6 +4079,54 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3620,8 +4141,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3647,6 +4171,142 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비-건물</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>감가상각비-공구와기구</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>감가상각비-구축물</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>감가상각비-기계장치</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>감가상각비-비품</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>감가상각비-차량운반구</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>유형자산처분손실</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -4348,8 +5008,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20.25" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="17.08203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="19.08203125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="4.83203125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4385,6 +5054,134 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>건물 감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>공구와기구</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>공구와기구 감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>공구와기구</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>국고보조금(공구)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>구축물 감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>국고보조금(구축물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>기계장치 감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>국고보조금(기계)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>비품 감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차량운반구 감가상각누계액</t>
         </is>
       </c>
     </row>
@@ -4399,8 +5196,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="2"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="4.83203125" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4421,6 +5223,23 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>유형자산처분손실</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5131,119 +5950,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>외화외상매출금</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>받을어음</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>부도어음</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>외상매입금</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>상품매출-국내</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>상품매출-수출</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>제품매출-국내</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>제품매출-수출</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5305,6 +6011,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5327,6 +6038,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5349,6 +6065,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5371,6 +6092,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5389,6 +6115,11 @@
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -5697,7 +6428,154 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5849,154 +6727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>제품매출-국내</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>제품매출-수출</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>상품매출-국내</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>상품매출-수출</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>외상매입금</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="C9" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6144,4 +6875,1073 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>삼동소재</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>삼동소재(2공장)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>금화화학</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="23" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>비용구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>상품매출-국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>상품매출-수출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>제품매출-국내</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>제품매출-수출</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>반제품매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MB매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>부산물매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>교육훈련비</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>도서인쇄비</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>복리후생비-경조비</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>복리후생비-기숙사운영</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>복리후생비-기타</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>복리후생비-선물비</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>복리후생비-식당운영</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>복리후생비-식대</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>복리후생비-행사비</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>소모품비-공구소모품</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>소모품비-기타</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>소모품비-사무용품</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>소모품비-생산소모품</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>소모품비-전산용품</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>수도광열비-MB실</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>수도광열비-기숙사</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>수도광열비-기타</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>수도광열비-식당</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>수선비-건물</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>수선비-공구와기구</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>수선비-구축물</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>수선비-기계장치</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>수선비-기타</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>여비교통비-교통비</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>여비교통비-기타</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>여비교통비-숙박비</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>여비교통비-식대</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>운반비-원료</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>운반비-제품</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>전력비</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>접대비-경조사</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>접대비-기타</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>접대비-별도</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>접대비-식대등</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>접대비-주대</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>접대비-체력단련</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>지급수수료-계통</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>지급수수료-기타</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>지급수수료-수탁수수료</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>지급수수료-안전관리</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>지급수수료-용역료</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>지급수수료-은행수수료</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>지급수수료-자문료</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>지급수수료-장려금</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>지급수수료-재활용분담금</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>지급수수료-파렛트사용료</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>지급수수료-판매</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>지급임차료</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>포장비</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>회의비</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>